--- a/clases/Ticket de Salida - Trazabilidad.xlsx
+++ b/clases/Ticket de Salida - Trazabilidad.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I436"/>
+  <dimension ref="A1:I593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17903,6 +17903,6539 @@
       </c>
       <c r="I436" t="inlineStr"/>
     </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:15</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Maura Isabel Muñoz Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>1</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:15</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Maura Isabel Muñoz Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>2</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:15</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Maura Isabel Muñoz Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>3</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:15</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Maura Isabel Muñoz Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:25</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Luckas Martín Letelier Lavín</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>1</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:25</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Luckas Martín Letelier Lavín</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>2</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:25</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Luckas Martín Letelier Lavín</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>3</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:25</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Luckas Martín Letelier Lavín</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:26</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Damián Cristóbal Flores Silva</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>1</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:26</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Damián Cristóbal Flores Silva</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>2</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:26</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Damián Cristóbal Flores Silva</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>3</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:26</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Damián Cristóbal Flores Silva</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:30</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Diego Pablo Vargas Jaqui</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>1</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:30</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Diego Pablo Vargas Jaqui</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>2</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:30</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Diego Pablo Vargas Jaqui</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>3</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:30</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Diego Pablo Vargas Jaqui</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:32</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Diego Andrés Donoso Figueroa</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>1</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:32</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Diego Andrés Donoso Figueroa</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>2</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:32</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Diego Andrés Donoso Figueroa</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>3</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:32</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Diego Andrés Donoso Figueroa</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:32</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Felipe Alejandro Román Brito</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>1</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:32</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Felipe Alejandro Román Brito</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>2</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:32</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Felipe Alejandro Román Brito</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>3</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:32</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Felipe Alejandro Román Brito</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:34</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>1</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:34</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>2</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:34</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>3</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:34</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:34</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Simón Abrahams Delgado</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>1</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:34</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Simón Abrahams Delgado</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>2</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:34</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Simón Abrahams Delgado</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>3</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:34</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Simón Abrahams Delgado</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:37</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Diego Antonio Peña Bustamante</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>1</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:37</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Diego Antonio Peña Bustamante</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>2</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:37</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Diego Antonio Peña Bustamante</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>3</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:37</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Diego Antonio Peña Bustamante</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:38</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Francisco Ignacio Vega Sanhueza</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>1</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:38</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Francisco Ignacio Vega Sanhueza</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>2</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:38</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Francisco Ignacio Vega Sanhueza</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>3</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:38</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Francisco Ignacio Vega Sanhueza</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:42</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Héctor Mauricio Vergara Alarcón</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>1</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:42</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Héctor Mauricio Vergara Alarcón</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>2</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:42</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Héctor Mauricio Vergara Alarcón</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>3</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:42</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Héctor Mauricio Vergara Alarcón</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:45</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Sebastián Andrés Ulloa Cuevas</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>1</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:45</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Sebastián Andrés Ulloa Cuevas</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>2</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:45</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Sebastián Andrés Ulloa Cuevas</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>3</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:45</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Sebastián Andrés Ulloa Cuevas</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:52</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Eduardo Eleazarth Pacco Ríos</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>1</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:52</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Eduardo Eleazarth Pacco Ríos</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>2</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:52</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Eduardo Eleazarth Pacco Ríos</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>3</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:52</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Eduardo Eleazarth Pacco Ríos</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:53</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Vicente Ignacio Benítez Muñoz</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>1</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:53</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Vicente Ignacio Benítez Muñoz</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>2</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:53</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Vicente Ignacio Benítez Muñoz</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>3</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:53</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Vicente Ignacio Benítez Muñoz</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:55</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Julián Alonso Sandoval Arriagada</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>1</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:55</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Julián Alonso Sandoval Arriagada</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>2</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:55</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Julián Alonso Sandoval Arriagada</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>3</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:08:55</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Julián Alonso Sandoval Arriagada</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:02</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Alain Israel Moyano Molina</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>1</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:02</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Alain Israel Moyano Molina</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>2</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:02</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Alain Israel Moyano Molina</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>3</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:02</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Alain Israel Moyano Molina</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:08</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Santino Garcia Colombati</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>1</v>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:08</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Santino Garcia Colombati</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>2</v>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:08</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Santino Garcia Colombati</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>3</v>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:08</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Santino Garcia Colombati</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:14</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>1</v>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:14</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>2</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:14</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>3</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>18/08/2026 17:09:14</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:32:31</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Benjamín Esteban Mejías González</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:46</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Martín Natahel Sánchez Orellana</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>1</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:46</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Martín Natahel Sánchez Orellana</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>2</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:46</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Martín Natahel Sánchez Orellana</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>3</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:46</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Martín Natahel Sánchez Orellana</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:55</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Héctor Mauricio Vergara Alarcón</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>1</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:55</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Héctor Mauricio Vergara Alarcón</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>2</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:55</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Héctor Mauricio Vergara Alarcón</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>3</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:55</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Héctor Mauricio Vergara Alarcón</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:56</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Francisco Ignacio Vega Sanhueza</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>1</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:56</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Francisco Ignacio Vega Sanhueza</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>2</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:56</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Francisco Ignacio Vega Sanhueza</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>3</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:56</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Francisco Ignacio Vega Sanhueza</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:57</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Cristóbal Alonso Muñoz Cubillos</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>1</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:57</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Cristóbal Alonso Muñoz Cubillos</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>2</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:57</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Cristóbal Alonso Muñoz Cubillos</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>3</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:57</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Cristóbal Alonso Muñoz Cubillos</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:57</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Diego Pablo Vargas Jaqui</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>1</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:57</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Diego Pablo Vargas Jaqui</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>2</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:57</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Diego Pablo Vargas Jaqui</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>3</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:57</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Diego Pablo Vargas Jaqui</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:58</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Eduardo Eleazarth Pacco Ríos</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>1</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:58</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Eduardo Eleazarth Pacco Ríos</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>2</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:58</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Eduardo Eleazarth Pacco Ríos</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>3</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:58</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Eduardo Eleazarth Pacco Ríos</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:59</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Diego Andrés Donoso Figueroa</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>1</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:59</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Diego Andrés Donoso Figueroa</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>2</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:59</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Diego Andrés Donoso Figueroa</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>3</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:36:59</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Diego Andrés Donoso Figueroa</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Julián Rafael Aravena Sagal</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>1</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Julián Rafael Aravena Sagal</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>2</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Julián Rafael Aravena Sagal</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>3</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Julián Rafael Aravena Sagal</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:02</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Sebastián Andrés Ulloa Cuevas</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>1</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:02</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Sebastián Andrés Ulloa Cuevas</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>2</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:02</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Sebastián Andrés Ulloa Cuevas</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>3</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:02</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Sebastián Andrés Ulloa Cuevas</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:02</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>1</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:02</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>2</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:02</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>3</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:02</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Alex Saravia Lara</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:05</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Santino Garcia Colombati</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>1</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:05</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Santino Garcia Colombati</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>2</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:05</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Santino Garcia Colombati</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>3</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:05</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Santino Garcia Colombati</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:06</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Vicente Ignacio Benítez Muñoz</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>1</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:06</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Vicente Ignacio Benítez Muñoz</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>2</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:06</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Vicente Ignacio Benítez Muñoz</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>3</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:06</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Vicente Ignacio Benítez Muñoz</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:07</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Luckas Martín Letelier Lavín</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>1</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:07</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Luckas Martín Letelier Lavín</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>2</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:07</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Luckas Martín Letelier Lavín</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>3</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:07</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Luckas Martín Letelier Lavín</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:10</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Maura Isabel Muñoz Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>1</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:10</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Maura Isabel Muñoz Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>2</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:10</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Maura Isabel Muñoz Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>3</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:10</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Maura Isabel Muñoz Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:14</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Diego Antonio Peña Bustamante</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>1</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:14</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Diego Antonio Peña Bustamante</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>2</v>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:14</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Diego Antonio Peña Bustamante</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>3</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:14</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Diego Antonio Peña Bustamante</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:16</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Felipe Aravena Cárdenas</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>1</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:16</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Felipe Aravena Cárdenas</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>2</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:16</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Felipe Aravena Cárdenas</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>3</v>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:16</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Felipe Aravena Cárdenas</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:21</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Diego Alonso Cifuentes Tessada</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>1</v>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:21</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Diego Alonso Cifuentes Tessada</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>2</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:21</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Diego Alonso Cifuentes Tessada</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>3</v>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:21</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Diego Alonso Cifuentes Tessada</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:23</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Alain Israel Moyano Molina</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>1</v>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:23</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Alain Israel Moyano Molina</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>2</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:23</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Alain Israel Moyano Molina</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>3</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:23</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Alain Israel Moyano Molina</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:28</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Felipe Alejandro Román Brito</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>1</v>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:28</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Felipe Alejandro Román Brito</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>2</v>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:28</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Felipe Alejandro Román Brito</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>3</v>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:28</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Felipe Alejandro Román Brito</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:31</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Víctor Alonso Olguín</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>1</v>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>funciones uso retorno (funciones)</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:31</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Víctor Alonso Olguín</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>2</v>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>funciones uso retorno (funciones)</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:31</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Víctor Alonso Olguín</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>3</v>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>funciones uso retorno (funciones)</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:31</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Víctor Alonso Olguín</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>funciones uso retorno (funciones)</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:49</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Vicente Narváez Fernandez</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>1</v>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:49</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Vicente Narváez Fernandez</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>2</v>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:49</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Vicente Narváez Fernandez</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>3</v>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>20/08/2026 15:37:49</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Vicente Narváez Fernandez</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Comprensión objetivo (1-5)</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17914,7 +24447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -17932,6 +24465,10 @@
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17972,40 +24509,60 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>Clase 24a - funciones def</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Clase 24b - funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>% acierto global</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Comprensión Clase 16 (1-5)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Comprensión Clase 19.5 (1-5)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Comprensión Clase 20 (1-5)</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Comprensión Clase 21 (1-5)</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Comprensión Clase 21.5 (1-5)</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Comprensión Clase 22 (1-5)</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Comprensión Clase 24a (1-5)</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Comprensión Clase 24b (1-5)</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Comprensión promedio global</t>
         </is>
@@ -18044,35 +24601,47 @@
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="Q2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" s="4" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -18103,30 +24672,42 @@
         <v>0.67</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I3" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="n">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="P3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O3" s="4" t="n">
-        <v>2.8</v>
+      <c r="Q3" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -18161,19 +24742,19 @@
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>—</t>
@@ -18184,15 +24765,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>1</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O4" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="P4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18228,22 +24827,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>0.33</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>—</t>
@@ -18259,7 +24858,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18289,33 +24908,49 @@
       <c r="G6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I6" s="4" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="n">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="n">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O6" s="4" t="n">
-        <v>3.75</v>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="7">
@@ -18347,34 +24982,50 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I7" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="n">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>2.33</v>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="8">
@@ -18409,37 +25060,53 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="n">
+      <c r="J8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>2</v>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>2.33</v>
       </c>
     </row>
     <row r="9">
@@ -18469,15 +25136,13 @@
         <v>0.33</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.33</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0.45</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>1</v>
@@ -18488,13 +25153,27 @@
         </is>
       </c>
       <c r="M9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O9" s="4" t="n">
-        <v>1.5</v>
+      <c r="Q9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="10">
@@ -18522,30 +25201,42 @@
         <v>1</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I10" s="4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="n">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="O10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="P10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O10" s="4" t="n">
-        <v>3.2</v>
+      <c r="Q10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>2.86</v>
       </c>
     </row>
     <row r="11">
@@ -18579,34 +25270,46 @@
         <v>0.33</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I11" s="4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="n">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O11" s="4" t="n">
-        <v>3.33</v>
+      <c r="Q11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
@@ -18634,30 +25337,42 @@
         <v>1</v>
       </c>
       <c r="H12" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>0.85</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
       </c>
       <c r="K12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="N12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="P12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O12" s="4" t="n">
-        <v>4.4</v>
+      <c r="Q12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>4.57</v>
       </c>
     </row>
     <row r="13">
@@ -18687,32 +25402,44 @@
         <v>1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I13" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="n">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
       </c>
       <c r="N13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O13" s="4" t="n">
-        <v>4.25</v>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>4.17</v>
       </c>
     </row>
     <row r="14">
@@ -18745,35 +25472,51 @@
       <c r="G14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="J14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="n">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O14" s="4" t="n">
-        <v>3.67</v>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -18801,30 +25544,42 @@
         <v>1</v>
       </c>
       <c r="H15" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="K15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="n">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="O15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="P15" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O15" s="4" t="n">
-        <v>3.8</v>
+      <c r="Q15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>3.43</v>
       </c>
     </row>
     <row r="16">
@@ -18851,31 +25606,47 @@
       <c r="G16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.77</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="O16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="P16" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O16" s="4" t="n">
-        <v>3.8</v>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>3.29</v>
       </c>
     </row>
     <row r="17">
@@ -18903,30 +25674,46 @@
         <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I17" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K17" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="n">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>4</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.8</v>
+        <v>4</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>3.83</v>
       </c>
     </row>
     <row r="18">
@@ -18957,16 +25744,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>4</v>
@@ -18977,15 +25764,31 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v>3.67</v>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
@@ -19016,32 +25819,52 @@
       <c r="G19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>0.57</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="n">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -19072,30 +25895,42 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="I20" s="4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="n">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="N20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="O20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="P20" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="O20" s="4" t="n">
-        <v>3</v>
+      <c r="Q20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>2.71</v>
       </c>
     </row>
     <row r="21">
@@ -19130,37 +25965,53 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I21" s="4" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K21" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>2.5</v>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>2.33</v>
       </c>
     </row>
     <row r="22">
@@ -19194,35 +26045,47 @@
         <v>1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O22" s="4" t="n">
+      <c r="Q22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19255,34 +26118,46 @@
         <v>1</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I23" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="n">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O23" s="4" t="n">
-        <v>4.33</v>
+      <c r="Q23" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="24">
@@ -19311,33 +26186,49 @@
       <c r="G24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I24" s="4" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K24" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="n">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="n">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="P24" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O24" s="4" t="n">
-        <v>2.75</v>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>2.67</v>
       </c>
     </row>
     <row r="25">
@@ -19380,10 +26271,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J25" s="3" t="n">
+        <v>0.33</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -19395,8 +26284,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M25" s="4" t="n">
-        <v>3</v>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -19406,6 +26297,22 @@
       <c r="O25" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19439,22 +26346,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
         <v>0.33</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="K26" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>—</t>
@@ -19470,7 +26377,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O26" s="4" t="n">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -19501,148 +26428,277 @@
         <v>0.33</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="I27" s="4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="n">
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="n">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="P27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="O27" s="4" t="n">
-        <v>3.25</v>
+      <c r="Q27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>3.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Vicente Narváez Fernandez</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Víctor Alonso Olguín</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>0.33</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="n">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="O29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Promedio curso</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B30" s="6" t="n">
         <v>0.68</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C30" s="6" t="n">
         <v>0.55</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D30" s="6" t="n">
         <v>0.76</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E30" s="6" t="n">
         <v>0.71</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F30" s="6" t="n">
         <v>0.78</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G30" s="6" t="n">
         <v>0.79</v>
       </c>
-      <c r="H29" s="6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I29" s="7" t="n">
+      <c r="H30" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K30" s="7" t="n">
         <v>2.95</v>
       </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="n">
         <v>3.05</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="N30" s="7" t="n">
         <v>3.21</v>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="O30" s="7" t="n">
         <v>3.12</v>
       </c>
-      <c r="N29" s="7" t="n">
+      <c r="P30" s="7" t="n">
         <v>3.37</v>
       </c>
-      <c r="O29" s="7" t="n">
-        <v>3.13</v>
+      <c r="Q30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" s="7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S30" s="7" t="n">
+        <v>3.01</v>
       </c>
     </row>
   </sheetData>
@@ -19656,7 +26712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19894,33 +26950,97 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>24a</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>funciones def</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>24b</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>funciones uso retorno</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Promedio general</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C10" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E10" s="6" t="n">
         <v>0.68</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="F10" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>89</v>
+      <c r="G10" s="7" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
